--- a/artfynd/A 30991-2024 artfynd.xlsx
+++ b/artfynd/A 30991-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119270211</v>
+        <v>119270215</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494536</v>
+        <v>494527</v>
       </c>
       <c r="R2" t="n">
-        <v>6959594</v>
+        <v>6959645</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119270219</v>
+        <v>119270216</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494735</v>
+        <v>494595</v>
       </c>
       <c r="R3" t="n">
-        <v>6959437</v>
+        <v>6959581</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119270216</v>
+        <v>119270217</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494595</v>
+        <v>494643</v>
       </c>
       <c r="R4" t="n">
-        <v>6959581</v>
+        <v>6959568</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119270224</v>
+        <v>119270211</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494563</v>
+        <v>494536</v>
       </c>
       <c r="R5" t="n">
-        <v>6959746</v>
+        <v>6959594</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,37 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119270212</v>
+        <v>119270222</v>
       </c>
       <c r="B6" t="n">
-        <v>97825</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494595</v>
+        <v>494506</v>
       </c>
       <c r="R6" t="n">
-        <v>6959692</v>
+        <v>6959599</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,37 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119270213</v>
+        <v>119270212</v>
       </c>
       <c r="B7" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99036</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>223591</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494714</v>
+        <v>494595</v>
       </c>
       <c r="R7" t="n">
-        <v>6959506</v>
+        <v>6959692</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,37 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119270222</v>
+        <v>119270213</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494506</v>
+        <v>494714</v>
       </c>
       <c r="R8" t="n">
-        <v>6959599</v>
+        <v>6959506</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,12 +1362,7 @@
         <v>119270214</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,15 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119270217</v>
+        <v>119270218</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1536,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494643</v>
+        <v>494683</v>
       </c>
       <c r="R10" t="n">
-        <v>6959568</v>
+        <v>6959451</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,15 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119270215</v>
+        <v>119270219</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1638,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494527</v>
+        <v>494735</v>
       </c>
       <c r="R11" t="n">
-        <v>6959645</v>
+        <v>6959437</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 30991-2024 artfynd.xlsx
+++ b/artfynd/A 30991-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119270213</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119270214</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119270215</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119270216</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119270217</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119270218</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119270219</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119270211</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119270222</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,8 +1697,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119270212</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>